--- a/output/yearly_total_coral_cover_iteration_91_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_91_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.25687899864306</v>
+        <v>1.278919234603401</v>
       </c>
       <c r="C3" t="n">
-        <v>4.601281538512128</v>
+        <v>4.60745673157184</v>
       </c>
       <c r="D3" t="n">
-        <v>6.063779515430627</v>
+        <v>6.039824871447006</v>
       </c>
       <c r="E3" t="n">
-        <v>11.92194005258581</v>
+        <v>11.92620083762225</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.384049551445724</v>
+        <v>1.442727878531297</v>
       </c>
       <c r="C4" t="n">
-        <v>5.080887715471485</v>
+        <v>5.086872537964096</v>
       </c>
       <c r="D4" t="n">
-        <v>6.263605942724143</v>
+        <v>6.278891668220765</v>
       </c>
       <c r="E4" t="n">
-        <v>12.72854320964135</v>
+        <v>12.80849208471616</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.549697158323928</v>
+        <v>1.656112311005712</v>
       </c>
       <c r="C5" t="n">
-        <v>5.720037138519697</v>
+        <v>5.675798034303142</v>
       </c>
       <c r="D5" t="n">
-        <v>6.538085984203553</v>
+        <v>6.607953575486249</v>
       </c>
       <c r="E5" t="n">
-        <v>13.80782028104718</v>
+        <v>13.9398639207951</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.741133745109746</v>
+        <v>1.888656740473674</v>
       </c>
       <c r="C6" t="n">
-        <v>6.52883727947918</v>
+        <v>6.401013437691791</v>
       </c>
       <c r="D6" t="n">
-        <v>6.932808038820405</v>
+        <v>7.011040280230453</v>
       </c>
       <c r="E6" t="n">
-        <v>15.20277906340933</v>
+        <v>15.30071045839592</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.960027348883661</v>
+        <v>2.137117190159748</v>
       </c>
       <c r="C7" t="n">
-        <v>7.467439162159331</v>
+        <v>7.291930052257706</v>
       </c>
       <c r="D7" t="n">
-        <v>7.428453830388433</v>
+        <v>7.44942806827551</v>
       </c>
       <c r="E7" t="n">
-        <v>16.85592034143142</v>
+        <v>16.87847531069296</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.194893420570726</v>
+        <v>1.313205760974037</v>
       </c>
       <c r="C8" t="n">
-        <v>5.124038650749804</v>
+        <v>4.997949973747112</v>
       </c>
       <c r="D8" t="n">
-        <v>5.66451130184702</v>
+        <v>5.691233463410754</v>
       </c>
       <c r="E8" t="n">
-        <v>11.98344337316755</v>
+        <v>12.0023891981319</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.503266672796781</v>
+        <v>1.631894804988483</v>
       </c>
       <c r="C9" t="n">
-        <v>6.282837194095979</v>
+        <v>6.159671027719416</v>
       </c>
       <c r="D9" t="n">
-        <v>6.183870974934353</v>
+        <v>6.183344117211576</v>
       </c>
       <c r="E9" t="n">
-        <v>13.96997484182711</v>
+        <v>13.97490994991947</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.838205953308014</v>
+        <v>1.978093683616225</v>
       </c>
       <c r="C10" t="n">
-        <v>7.623144524624101</v>
+        <v>7.461472923502458</v>
       </c>
       <c r="D10" t="n">
-        <v>6.735389304063081</v>
+        <v>6.68596662456138</v>
       </c>
       <c r="E10" t="n">
-        <v>16.1967397819952</v>
+        <v>16.12553323168006</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.169994020074938</v>
+        <v>2.342903219835589</v>
       </c>
       <c r="C11" t="n">
-        <v>9.083223067293286</v>
+        <v>8.891931626865874</v>
       </c>
       <c r="D11" t="n">
-        <v>7.27803809486652</v>
+        <v>7.168563995161859</v>
       </c>
       <c r="E11" t="n">
-        <v>18.53125518223474</v>
+        <v>18.40339884186332</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.511759715617372</v>
+        <v>2.724684747648919</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63348284644609</v>
+        <v>10.44757900303439</v>
       </c>
       <c r="D12" t="n">
-        <v>7.91408108369107</v>
+        <v>7.729953880439182</v>
       </c>
       <c r="E12" t="n">
-        <v>21.05932364575454</v>
+        <v>20.90221763112249</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.831995879146748</v>
+        <v>3.097436297790999</v>
       </c>
       <c r="C13" t="n">
-        <v>12.23765996544672</v>
+        <v>12.06773909980703</v>
       </c>
       <c r="D13" t="n">
-        <v>8.463714510645692</v>
+        <v>8.230032699339613</v>
       </c>
       <c r="E13" t="n">
-        <v>23.53337035523916</v>
+        <v>23.39520809693764</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.625882190480185</v>
+        <v>1.797354244503933</v>
       </c>
       <c r="C14" t="n">
-        <v>8.604576841256382</v>
+        <v>8.493963327418893</v>
       </c>
       <c r="D14" t="n">
-        <v>6.456021990512237</v>
+        <v>6.245623640015103</v>
       </c>
       <c r="E14" t="n">
-        <v>16.6864810222488</v>
+        <v>16.53694121193793</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.664170350945811</v>
+        <v>1.855738780475491</v>
       </c>
       <c r="C15" t="n">
-        <v>9.323225978242089</v>
+        <v>9.262995756586548</v>
       </c>
       <c r="D15" t="n">
-        <v>6.523477875271036</v>
+        <v>6.272749329083442</v>
       </c>
       <c r="E15" t="n">
-        <v>17.51087420445894</v>
+        <v>17.39148386614548</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.936065377636965</v>
+        <v>2.172666574360446</v>
       </c>
       <c r="C16" t="n">
-        <v>11.00723745029073</v>
+        <v>11.04946241905039</v>
       </c>
       <c r="D16" t="n">
-        <v>7.026751200899079</v>
+        <v>6.729222741650039</v>
       </c>
       <c r="E16" t="n">
-        <v>19.97005402882677</v>
+        <v>19.95135173506087</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.560978849752429</v>
+        <v>1.754078805700733</v>
       </c>
       <c r="C17" t="n">
-        <v>10.1381354776292</v>
+        <v>10.29290800320371</v>
       </c>
       <c r="D17" t="n">
-        <v>6.5568278447843</v>
+        <v>6.245702179831444</v>
       </c>
       <c r="E17" t="n">
-        <v>18.25594217216593</v>
+        <v>18.29268898873589</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.785111850631976</v>
+        <v>2.018002041033404</v>
       </c>
       <c r="C18" t="n">
-        <v>11.76935837562049</v>
+        <v>12.08194684465267</v>
       </c>
       <c r="D18" t="n">
-        <v>7.012496224233414</v>
+        <v>6.683610743310733</v>
       </c>
       <c r="E18" t="n">
-        <v>20.56696645048588</v>
+        <v>20.78355962899681</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.793211269192012</v>
+        <v>2.036066198791545</v>
       </c>
       <c r="C19" t="n">
-        <v>12.52079788592804</v>
+        <v>12.98940570011912</v>
       </c>
       <c r="D19" t="n">
-        <v>7.132151634427016</v>
+        <v>6.776582250902905</v>
       </c>
       <c r="E19" t="n">
-        <v>21.44616078954706</v>
+        <v>21.80205414981357</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.997886030573387</v>
+        <v>2.276967450459627</v>
       </c>
       <c r="C20" t="n">
-        <v>14.33565669199869</v>
+        <v>14.96893304862309</v>
       </c>
       <c r="D20" t="n">
-        <v>7.582479306365029</v>
+        <v>7.26458939972991</v>
       </c>
       <c r="E20" t="n">
-        <v>23.91602202893711</v>
+        <v>24.51048989881263</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.187885269707513</v>
+        <v>1.361360089047925</v>
       </c>
       <c r="C21" t="n">
-        <v>10.47577814807376</v>
+        <v>11.02648952277101</v>
       </c>
       <c r="D21" t="n">
-        <v>6.349796888912733</v>
+        <v>6.072983306223303</v>
       </c>
       <c r="E21" t="n">
-        <v>18.01346030669401</v>
+        <v>18.46083291804224</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_91_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_91_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.278919234603401</v>
+        <v>1.249270453935147</v>
       </c>
       <c r="C3" t="n">
-        <v>4.60745673157184</v>
+        <v>4.692525170144826</v>
       </c>
       <c r="D3" t="n">
-        <v>6.039824871447006</v>
+        <v>6.065684105976866</v>
       </c>
       <c r="E3" t="n">
-        <v>11.92620083762225</v>
+        <v>12.00747973005684</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.442727878531297</v>
+        <v>1.369917325455395</v>
       </c>
       <c r="C4" t="n">
-        <v>5.086872537964096</v>
+        <v>5.29690327522442</v>
       </c>
       <c r="D4" t="n">
-        <v>6.278891668220765</v>
+        <v>6.260717875767392</v>
       </c>
       <c r="E4" t="n">
-        <v>12.80849208471616</v>
+        <v>12.92753847644721</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.656112311005712</v>
+        <v>1.541336803657433</v>
       </c>
       <c r="C5" t="n">
-        <v>5.675798034303142</v>
+        <v>6.068772345948032</v>
       </c>
       <c r="D5" t="n">
-        <v>6.607953575486249</v>
+        <v>6.575950280298961</v>
       </c>
       <c r="E5" t="n">
-        <v>13.9398639207951</v>
+        <v>14.18605942990443</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.888656740473674</v>
+        <v>1.729670847698874</v>
       </c>
       <c r="C6" t="n">
-        <v>6.401013437691791</v>
+        <v>6.995746994422873</v>
       </c>
       <c r="D6" t="n">
-        <v>7.011040280230453</v>
+        <v>6.836488068297474</v>
       </c>
       <c r="E6" t="n">
-        <v>15.30071045839592</v>
+        <v>15.56190591041922</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.137117190159748</v>
+        <v>1.935699877141753</v>
       </c>
       <c r="C7" t="n">
-        <v>7.291930052257706</v>
+        <v>8.052920440081502</v>
       </c>
       <c r="D7" t="n">
-        <v>7.44942806827551</v>
+        <v>7.136316765903823</v>
       </c>
       <c r="E7" t="n">
-        <v>16.87847531069296</v>
+        <v>17.12493708312708</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.313205760974037</v>
+        <v>1.15765001169243</v>
       </c>
       <c r="C8" t="n">
-        <v>4.997949973747112</v>
+        <v>5.633120948239277</v>
       </c>
       <c r="D8" t="n">
-        <v>5.691233463410754</v>
+        <v>5.27323727999098</v>
       </c>
       <c r="E8" t="n">
-        <v>12.0023891981319</v>
+        <v>12.06400823992269</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.631894804988483</v>
+        <v>1.43539277007529</v>
       </c>
       <c r="C9" t="n">
-        <v>6.159671027719416</v>
+        <v>6.972239886924003</v>
       </c>
       <c r="D9" t="n">
-        <v>6.183344117211576</v>
+        <v>5.654716374924314</v>
       </c>
       <c r="E9" t="n">
-        <v>13.97490994991947</v>
+        <v>14.06234903192361</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.978093683616225</v>
+        <v>1.723070189205851</v>
       </c>
       <c r="C10" t="n">
-        <v>7.461472923502458</v>
+        <v>8.493827011662717</v>
       </c>
       <c r="D10" t="n">
-        <v>6.68596662456138</v>
+        <v>6.125593224067726</v>
       </c>
       <c r="E10" t="n">
-        <v>16.12553323168006</v>
+        <v>16.34249042493629</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.342903219835589</v>
+        <v>2.014572775470413</v>
       </c>
       <c r="C11" t="n">
-        <v>8.891931626865874</v>
+        <v>10.12328542677652</v>
       </c>
       <c r="D11" t="n">
-        <v>7.168563995161859</v>
+        <v>6.545809669467481</v>
       </c>
       <c r="E11" t="n">
-        <v>18.40339884186332</v>
+        <v>18.68366787171441</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.724684747648919</v>
+        <v>2.301739231222062</v>
       </c>
       <c r="C12" t="n">
-        <v>10.44757900303439</v>
+        <v>11.8118391525209</v>
       </c>
       <c r="D12" t="n">
-        <v>7.729953880439182</v>
+        <v>6.941704969237501</v>
       </c>
       <c r="E12" t="n">
-        <v>20.90221763112249</v>
+        <v>21.05528335298046</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.097436297790999</v>
+        <v>2.574231243801761</v>
       </c>
       <c r="C13" t="n">
-        <v>12.06773909980703</v>
+        <v>13.50073744416997</v>
       </c>
       <c r="D13" t="n">
-        <v>8.230032699339613</v>
+        <v>7.327043787402123</v>
       </c>
       <c r="E13" t="n">
-        <v>23.39520809693764</v>
+        <v>23.40201247537385</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.797354244503933</v>
+        <v>1.491647826878519</v>
       </c>
       <c r="C14" t="n">
-        <v>8.493963327418893</v>
+        <v>9.430049945941185</v>
       </c>
       <c r="D14" t="n">
-        <v>6.245623640015103</v>
+        <v>5.586154254641393</v>
       </c>
       <c r="E14" t="n">
-        <v>16.53694121193793</v>
+        <v>16.5078520274611</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.855738780475491</v>
+        <v>1.503006647816654</v>
       </c>
       <c r="C15" t="n">
-        <v>9.262995756586548</v>
+        <v>10.11402375401289</v>
       </c>
       <c r="D15" t="n">
-        <v>6.272749329083442</v>
+        <v>5.551488743204438</v>
       </c>
       <c r="E15" t="n">
-        <v>17.39148386614548</v>
+        <v>17.16851914503399</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.172666574360446</v>
+        <v>1.731518243457142</v>
       </c>
       <c r="C16" t="n">
-        <v>11.04946241905039</v>
+        <v>11.88941630237283</v>
       </c>
       <c r="D16" t="n">
-        <v>6.729222741650039</v>
+        <v>5.90117745798011</v>
       </c>
       <c r="E16" t="n">
-        <v>19.95135173506087</v>
+        <v>19.52211200381008</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.754078805700733</v>
+        <v>1.377558926167997</v>
       </c>
       <c r="C17" t="n">
-        <v>10.29290800320371</v>
+        <v>10.85819833130902</v>
       </c>
       <c r="D17" t="n">
-        <v>6.245702179831444</v>
+        <v>5.41426004910482</v>
       </c>
       <c r="E17" t="n">
-        <v>18.29268898873589</v>
+        <v>17.65001730658184</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.018002041033404</v>
+        <v>1.563531393783471</v>
       </c>
       <c r="C18" t="n">
-        <v>12.08194684465267</v>
+        <v>12.67077948270582</v>
       </c>
       <c r="D18" t="n">
-        <v>6.683610743310733</v>
+        <v>5.791987478313779</v>
       </c>
       <c r="E18" t="n">
-        <v>20.78355962899681</v>
+        <v>20.02629835480307</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.036066198791545</v>
+        <v>1.560458523469178</v>
       </c>
       <c r="C19" t="n">
-        <v>12.98940570011912</v>
+        <v>13.55594284780883</v>
       </c>
       <c r="D19" t="n">
-        <v>6.776582250902905</v>
+        <v>5.856213413125606</v>
       </c>
       <c r="E19" t="n">
-        <v>21.80205414981357</v>
+        <v>20.97261478440361</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.276967450459627</v>
+        <v>1.737212380141774</v>
       </c>
       <c r="C20" t="n">
-        <v>14.96893304862309</v>
+        <v>15.63089607316559</v>
       </c>
       <c r="D20" t="n">
-        <v>7.26458939972991</v>
+        <v>6.182065293642165</v>
       </c>
       <c r="E20" t="n">
-        <v>24.51048989881263</v>
+        <v>23.55017374694953</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.361360089047925</v>
+        <v>1.035930360044192</v>
       </c>
       <c r="C21" t="n">
-        <v>11.02648952277101</v>
+        <v>11.54504866015417</v>
       </c>
       <c r="D21" t="n">
-        <v>6.072983306223303</v>
+        <v>5.122406091586328</v>
       </c>
       <c r="E21" t="n">
-        <v>18.46083291804224</v>
+        <v>17.70338511178469</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_91_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_91_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.249270453935147</v>
+        <v>2.59372786911839</v>
       </c>
       <c r="C3" t="n">
-        <v>4.692525170144826</v>
+        <v>7.641440242838597</v>
       </c>
       <c r="D3" t="n">
-        <v>6.065684105976866</v>
+        <v>8.230558223426895</v>
       </c>
       <c r="E3" t="n">
-        <v>12.00747973005684</v>
+        <v>18.46572633538388</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.369917325455395</v>
+        <v>1.066476178472624</v>
       </c>
       <c r="C4" t="n">
-        <v>5.29690327522442</v>
+        <v>4.348267662462319</v>
       </c>
       <c r="D4" t="n">
-        <v>6.260717875767392</v>
+        <v>5.967808917823962</v>
       </c>
       <c r="E4" t="n">
-        <v>12.92753847644721</v>
+        <v>11.38255275875891</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.541336803657433</v>
+        <v>1.151033200946375</v>
       </c>
       <c r="C5" t="n">
-        <v>6.068772345948032</v>
+        <v>4.853050140032295</v>
       </c>
       <c r="D5" t="n">
-        <v>6.575950280298961</v>
+        <v>6.33081194316811</v>
       </c>
       <c r="E5" t="n">
-        <v>14.18605942990443</v>
+        <v>12.33489528414678</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.729670847698874</v>
+        <v>1.244726327139048</v>
       </c>
       <c r="C6" t="n">
-        <v>6.995746994422873</v>
+        <v>5.494449720873664</v>
       </c>
       <c r="D6" t="n">
-        <v>6.836488068297474</v>
+        <v>6.74322701687706</v>
       </c>
       <c r="E6" t="n">
-        <v>15.56190591041922</v>
+        <v>13.48240306488977</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.935699877141753</v>
+        <v>1.349841089753748</v>
       </c>
       <c r="C7" t="n">
-        <v>8.052920440081502</v>
+        <v>6.27567345118384</v>
       </c>
       <c r="D7" t="n">
-        <v>7.136316765903823</v>
+        <v>7.172676493876875</v>
       </c>
       <c r="E7" t="n">
-        <v>17.12493708312708</v>
+        <v>14.79819103481446</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.15765001169243</v>
+        <v>1.463997623424619</v>
       </c>
       <c r="C8" t="n">
-        <v>5.633120948239277</v>
+        <v>7.207419414597715</v>
       </c>
       <c r="D8" t="n">
-        <v>5.27323727999098</v>
+        <v>7.646741009690186</v>
       </c>
       <c r="E8" t="n">
-        <v>12.06400823992269</v>
+        <v>16.31815804771252</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.43539277007529</v>
+        <v>1.589968391225858</v>
       </c>
       <c r="C9" t="n">
-        <v>6.972239886924003</v>
+        <v>8.303155665787365</v>
       </c>
       <c r="D9" t="n">
-        <v>5.654716374924314</v>
+        <v>8.108248259892388</v>
       </c>
       <c r="E9" t="n">
-        <v>14.06234903192361</v>
+        <v>18.00137231690561</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.723070189205851</v>
+        <v>1.009383902121358</v>
       </c>
       <c r="C10" t="n">
-        <v>8.493827011662717</v>
+        <v>6.275144793481805</v>
       </c>
       <c r="D10" t="n">
-        <v>6.125593224067726</v>
+        <v>6.379720558938175</v>
       </c>
       <c r="E10" t="n">
-        <v>16.34249042493629</v>
+        <v>13.66424925454134</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.014572775470413</v>
+        <v>0.9466600412970294</v>
       </c>
       <c r="C11" t="n">
-        <v>10.12328542677652</v>
+        <v>6.630645454666618</v>
       </c>
       <c r="D11" t="n">
-        <v>6.545809669467481</v>
+        <v>6.294288873714618</v>
       </c>
       <c r="E11" t="n">
-        <v>18.68366787171441</v>
+        <v>13.87159436967826</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.301739231222062</v>
+        <v>1.022784758284327</v>
       </c>
       <c r="C12" t="n">
-        <v>11.8118391525209</v>
+        <v>7.850123365496795</v>
       </c>
       <c r="D12" t="n">
-        <v>6.941704969237501</v>
+        <v>6.760628850708895</v>
       </c>
       <c r="E12" t="n">
-        <v>21.05528335298046</v>
+        <v>15.63353697449002</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.574231243801761</v>
+        <v>0.8135154176470771</v>
       </c>
       <c r="C13" t="n">
-        <v>13.50073744416997</v>
+        <v>7.522887220717246</v>
       </c>
       <c r="D13" t="n">
-        <v>7.327043787402123</v>
+        <v>6.226293027718484</v>
       </c>
       <c r="E13" t="n">
-        <v>23.40201247537385</v>
+        <v>14.56269566608281</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.491647826878519</v>
+        <v>0.8854578894142833</v>
       </c>
       <c r="C14" t="n">
-        <v>9.430049945941185</v>
+        <v>8.827757546862809</v>
       </c>
       <c r="D14" t="n">
-        <v>5.586154254641393</v>
+        <v>6.647600237518961</v>
       </c>
       <c r="E14" t="n">
-        <v>16.5078520274611</v>
+        <v>16.36081567379605</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.503006647816654</v>
+        <v>0.8603447831396499</v>
       </c>
       <c r="C15" t="n">
-        <v>10.11402375401289</v>
+        <v>9.549734808565916</v>
       </c>
       <c r="D15" t="n">
-        <v>5.551488743204438</v>
+        <v>6.74207381909863</v>
       </c>
       <c r="E15" t="n">
-        <v>17.16851914503399</v>
+        <v>17.1521534108042</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.731518243457142</v>
+        <v>0.9528646867878693</v>
       </c>
       <c r="C16" t="n">
-        <v>11.88941630237283</v>
+        <v>11.25888883932031</v>
       </c>
       <c r="D16" t="n">
-        <v>5.90117745798011</v>
+        <v>7.286835802708143</v>
       </c>
       <c r="E16" t="n">
-        <v>19.52211200381008</v>
+        <v>19.49858932881633</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.377558926167997</v>
+        <v>0.5814597127942583</v>
       </c>
       <c r="C17" t="n">
-        <v>10.85819833130902</v>
+        <v>8.571501761100308</v>
       </c>
       <c r="D17" t="n">
-        <v>5.41426004910482</v>
+        <v>6.096466711308887</v>
       </c>
       <c r="E17" t="n">
-        <v>17.65001730658184</v>
+        <v>15.24942818520345</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.563531393783471</v>
+        <v>0.463708893146896</v>
       </c>
       <c r="C18" t="n">
-        <v>12.67077948270582</v>
+        <v>7.772526026953125</v>
       </c>
       <c r="D18" t="n">
-        <v>5.791987478313779</v>
+        <v>5.600095072041698</v>
       </c>
       <c r="E18" t="n">
-        <v>20.02629835480307</v>
+        <v>13.83632999214172</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.560458523469178</v>
+        <v>0.5502499532762524</v>
       </c>
       <c r="C19" t="n">
-        <v>13.55594284780883</v>
+        <v>9.749392839178588</v>
       </c>
       <c r="D19" t="n">
-        <v>5.856213413125606</v>
+        <v>6.172267451553783</v>
       </c>
       <c r="E19" t="n">
-        <v>20.97261478440361</v>
+        <v>16.47191024400862</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.737212380141774</v>
+        <v>0.6301740338789851</v>
       </c>
       <c r="C20" t="n">
-        <v>15.63089607316559</v>
+        <v>11.85346470144331</v>
       </c>
       <c r="D20" t="n">
-        <v>6.182065293642165</v>
+        <v>6.674539394523493</v>
       </c>
       <c r="E20" t="n">
-        <v>23.55017374694953</v>
+        <v>19.15817812984579</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.035930360044192</v>
+        <v>0.6982975070766714</v>
       </c>
       <c r="C21" t="n">
-        <v>11.54504866015417</v>
+        <v>14.08228724448667</v>
       </c>
       <c r="D21" t="n">
-        <v>5.122406091586328</v>
+        <v>7.198242889876911</v>
       </c>
       <c r="E21" t="n">
-        <v>17.70338511178469</v>
+        <v>21.97882764144025</v>
       </c>
     </row>
   </sheetData>
